--- a/archive/2026/2026-10-19.xlsx
+++ b/archive/2026/2026-10-19.xlsx
@@ -14,11 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_外資_上櫃" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_投信_上櫃" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_自營商_上櫃" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_外資_上市" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_投信_上市" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_自營商_上市" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_三大法人合計_上市" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2875,3654 +2871,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市自營商買賣超排行｜2026-10-19｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00632R</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>元大台灣50反1</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>41344</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-441670</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00680L</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>元大美債20正2</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>13608</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-226948</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00664R</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>9650</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-154200</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>00686R</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>群益臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>7046</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-112322</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>6815</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-90040</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>6239</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-61333</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>5157</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-60509</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>4837</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-59274</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>4776</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-40482</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>4253</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00673R</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P原油反1</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-33130</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>4170</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>主動野村台灣50</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-29610</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>009826</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>貝萊德世界股票</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3968</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-27530</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>3961</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-23936</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>3952</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-17530</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>3711</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-15531</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>3489</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-15520</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>2845</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>00922</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>國泰台灣領袖50</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-13652</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>2841</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-13027</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>2399</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-11969</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>00676R</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>富邦臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>2255</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-11537</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1980</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-10243</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1853</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-8626</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>00753L</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>中信中國50正2</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1853</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>00996A</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>主動兆豐台灣豐收</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-7716</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>00713</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>元大台灣高息低波</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1768</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>00984A</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>主動安聯台灣高息</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-6758</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>00708L</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P黃金正2</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1720</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-6518</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>00882</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>中信中國高股息</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1606</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-6411</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>00693U</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>期街口S&amp;P黃豆</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>1600</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-6088</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>1565</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>00934</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>中信成長高股息</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-5881</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>009820</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>元大納斯達克精選</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-5414</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1489</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-4937</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>00637L</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>元大滬深300正2</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>1399</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>00985B</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>群益ESG投等債0-5</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-4754</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1346</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-4155</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>1306</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>台新AI優息動能</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-3796</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>1248</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>00404A</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>主動聯博動能50</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-3598</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>1207</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>009803</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>玉山市值動能50</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-3496</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>00972</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>野村日本動能高息</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1195</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00410A</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>主動永豐科技趨勢</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-3227</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>1168</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>006208</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-3022</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>1105</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-3015</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>00946</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>群益科技高息成長</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>1097</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00712</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>復華富時不動產</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-3015</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>1034</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>國喬</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-2982</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>1021</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-2650</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>亞泥</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>965</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>00947</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>台新臺灣IC設計</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-1987</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>935</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>00662</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>富邦NASDAQ</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-1965</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>009813</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>貝萊德標普卓越50</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>933</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>00663L</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-1898</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>00642U</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P石油</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>886</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>00938</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>凱基優選30</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-1692</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>正新</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>829</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>00923</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>群益台ESG低碳50</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-1672</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>788</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-1632</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>009811</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>統一美國50</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>770</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>00909</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>國泰數位支付服務</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-1291</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>00715L</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>期街口布蘭特正2</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>739</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>00401A</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>主動摩根台灣鑫收</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-1274</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>00910</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>第一金太空衛星</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>725</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-1229</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市三大法人合計買賣超排行｜2026-10-19｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00632R</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>元大台灣50反1</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>43652</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-440650</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>15392</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-231093</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00680L</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>元大美債20正2</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>13258</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-167906</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>00664R</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>9647</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-110414</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>9580</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-98061</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>8652</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-93171</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>7412</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-84552</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>9105</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>泰金寶-DR</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>7160</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-59110</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>00686R</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>群益臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>7051</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-42201</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>6979</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-35323</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>6913</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00673R</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P原油反1</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-33129</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>6606</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-32423</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>5976</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-31106</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>5661</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>主動野村台灣50</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-27409</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>5250</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-24147</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>5150</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-23664</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>4515</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-23089</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>4495</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-21348</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>4409</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-21053</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>和益</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>4099</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-19006</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>009826</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>貝萊德世界股票</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>3968</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2312</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>金寶</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-15684</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>3935</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-15300</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>3860</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-15295</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>00985B</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>群益ESG投等債0-5</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>3660</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>00922</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>國泰台灣領袖50</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-15043</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>3393</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-15006</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>8039</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>台虹</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>3287</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-14535</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>4927</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>泰鼎-KY</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>3282</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-13521</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>正新</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>3261</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-11976</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>6269</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>台郡</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>3161</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-11817</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>潤泰新</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>3132</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-11233</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>2889</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-10400</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>2705</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-10375</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>敬鵬</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>2461</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-9505</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>5469</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>瀚宇博</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>2383</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-9406</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>00945B</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>凱基美國非投等債</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>2340</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-8637</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>00676R</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>富邦臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>2307</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00996A</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>主動兆豐台灣豐收</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-7676</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>2290</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-7206</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>2181</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>群益證</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-7205</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>00713</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>元大台灣高息低波</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>2176</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-7175</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>2135</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-7047</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>1974</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>00984A</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>主動安聯台灣高息</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-6786</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>009813</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>貝萊德標普卓越50</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>1810</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-6569</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>00693U</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>期街口S&amp;P黃豆</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>1770</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-5906</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>00882</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>中信中國高股息</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>1741</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>00934</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>中信成長高股息</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-5866</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>1728</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-5691</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2851</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>中再保</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>1722</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-5593</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>6834</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>天二科技</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>1654</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-5561</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>009820</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>元大納斯達克精選</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>1578</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>00712</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>復華富時不動產</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-5415</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>GIS-KY</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>1547</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-5410</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>1487</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>國喬</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-5338</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>本檔由程式自動抓取公開網頁整理，僅供參考，不構成投資建議。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>顏色慣例：紅色＝買超／上漲，綠色＝賣超／下跌。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -20093,3613 +16441,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市外資買賣超排行｜2026-10-19｜單位：張</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>本檔由程式自動抓取公開網頁整理，僅供參考，不構成投資建議。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>10021</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-46466</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>8762</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-36893</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>9105</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>泰金寶-DR</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>6719</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-29814</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>6665</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-24669</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>6064</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-24593</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>5745</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-22435</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>4900</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2312</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>金寶</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-15610</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>4195</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-14884</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>3968</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-13980</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>和益</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>3844</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-13706</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>3405</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-12009</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3344</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-11016</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>正新</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>3253</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-9835</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6269</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>台郡</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>3209</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-9616</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4927</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>泰鼎-KY</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>3197</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-8895</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>8039</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>台虹</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>3120</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-8521</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>2883</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-8386</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>2545</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-7490</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5469</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>瀚宇博</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>2311</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-7037</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>00632R</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>元大台灣50反1</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>2308</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-6967</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>00945B</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>凱基美國非投等債</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>2248</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-6750</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>主動野村台灣50</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2201</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>群益證</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-6450</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>敬鵬</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>2194</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-6259</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1978</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-5827</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>009819</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>中信數據及電力</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1952</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-5661</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1939</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-5642</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>1908</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-5523</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>1900</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-5052</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>潤泰新</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1752</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-4822</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2851</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>中再保</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1712</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-4663</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>6834</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>天二科技</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>1692</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>台中銀</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-4557</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1684</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-4204</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>GIS-KY</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>1608</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-4145</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>聯鈞</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>1600</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-4140</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>1599</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2820</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>華票</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-3824</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>正文</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1421</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>台亞</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-3786</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2883B</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>凱基金乙特</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>1378</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-3762</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3717</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>聯嘉投控</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>1250</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-3575</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>1173</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-3373</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>1076</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-3356</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3034</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>聯詠</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>1069</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-3346</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>8422</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>可寧衛*</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>1048</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-3323</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-3191</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>1008</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3576</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>聯合再生</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-3174</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>996</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-3062</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>台灣高鐵</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>981</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-3030</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>00991B</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>貝萊德A級公司債</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>925</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6209</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>今國光</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-2812</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>914</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>中環</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-2704</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>國產</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>910</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-2619</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>896</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-2549</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市投信買賣超排行｜2026-10-19｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>12775</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-4443</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00985B</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>群益ESG投等債0-5</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>8078</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-4222</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>7158</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-3970</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>5054</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-3012</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>4707</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-2770</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>4564</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-2699</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>3915</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-2039</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-1994</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>3141</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-1758</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>3064</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-1658</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>2789</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-1414</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>臺企銀</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>2747</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>聯鈞</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-1335</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>2417</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-1272</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>2415</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-1271</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>2356</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-1072</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>2287</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-1027</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>2173</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-989</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>2017</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-858</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>2014</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>致伸</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-837</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>1921</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>上銀</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-827</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>尖點</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1887</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>正新</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-821</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1789</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-795</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>台中銀</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1705</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-795</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1596</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>群益證</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-756</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>遠東銀</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1510</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>遠東新</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-716</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>華新科</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-674</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>潤泰新</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>1417</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-652</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>1214</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>日電貿</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-544</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1133</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-541</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>987</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>中纖</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-515</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3605</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>宏致</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>969</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-504</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>大成鋼</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>915</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>9958</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>世紀鋼</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-451</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>818</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>力麗</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-408</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>794</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8112</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>至上</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-401</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>735</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2501</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>國建</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-357</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>713</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>信邦</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-332</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>703</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>漢翔</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-319</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>台灣高鐵</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-317</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>658</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>8028</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>昇陽半導體</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-313</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2351</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>順德</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>651</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>力鵬</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-306</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>633</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-304</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>聯強</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>614</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3005</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>神基</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-291</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>573</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>00981T</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>平衡凱基雙核收息</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-270</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>550</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4763</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>材料*-KY</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-252</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2615</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>萬海</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>523</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-250</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>509</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>可成</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-238</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>中興電</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-228</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>485</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-220</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>454</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-213</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2539</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>櫻花建</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>433</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>群光</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-203</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>顏色慣例：紅色＝買超／上漲，綠色＝賣超／下跌。</t>
+        </is>
       </c>
     </row>
   </sheetData>
